--- a/src/main/resources/rewards.xlsx
+++ b/src/main/resources/rewards.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="146">
   <si>
     <t>饮食2（每天5大杯水，间隔2小时。早上两个鸡蛋）</t>
   </si>
@@ -450,6 +450,21 @@
   </si>
   <si>
     <t>2.5</t>
+  </si>
+  <si>
+    <t>2026年03月22日</t>
+  </si>
+  <si>
+    <t>2026年06月17日</t>
+  </si>
+  <si>
+    <t>22.0</t>
+  </si>
+  <si>
+    <t>25.8</t>
+  </si>
+  <si>
+    <t>-6.5</t>
   </si>
 </sst>
 </file>
@@ -1605,7 +1620,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="28.0"/>
@@ -3962,6 +3977,70 @@
         <v>140</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B97" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C97" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D97" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="E97" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="F97" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="G97" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="H97" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="I97" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="J97" t="s" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B98" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C98" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D98" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E98" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F98" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G98" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="H98" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I98" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="J98" t="s" s="0">
+        <v>145</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
